--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -13,13 +13,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03 Recommended BOM" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04 Evidence" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05 Decisions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 What 40k Buys" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06 Development Mule BOM" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'02 Options Compared'!$1:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'03 Recommended BOM'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'04 Evidence'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'05 Decisions'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'06 Development Mule BOM'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -163,7 +164,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -176,11 +177,20 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="hair">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -352,6 +362,43 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1129,15 +1176,16 @@
     <row r="45" ht="15" customHeight="1">
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>06 What ₹40k Buys</t>
+          <t>06 Development Mule BOM</t>
         </is>
       </c>
       <c r="C45" s="21" t="inlineStr">
         <is>
-          <t>A real ₹35,400 aircraft and the eight requirements it fails.</t>
-        </is>
-      </c>
-    </row>
+          <t>A buildable sub-₹50,000 aircraft with exact parts and links, and the eight requirements it fails.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
     <row r="47">
       <c r="B47" s="18" t="inlineStr">
         <is>
@@ -4936,33 +4984,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F44"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="66" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Development Mule — buildable BOM under ₹50,000</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>What ₹40,000 actually buys</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>A real, orderable aircraft. Every line has an exact part, an Indian supplier and a link. It CANNOT fly the NIDAR mission — see the bottom of this sheet — and is not meant to.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Specified so the answer can be checked. Not a cheaper RescueSwarm — a different, much smaller aircraft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr"/>
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>PURPOSE  Fly from week 1 of the flight-test window so the ₹2.6 L aircraft is not the only one exercising the ground station, the radio path and the failsafes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Item</t>
@@ -4970,588 +5033,1134 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Part class</t>
+          <t>Exact part / model</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
+          <t>Supplier</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="G5" s="7" t="inlineStr">
         <is>
           <t>Unit ₹</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Ext ₹</t>
         </is>
       </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="B6" s="76" t="inlineStr">
-        <is>
-          <t>Frame</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>450 mm CF/glass quad kit</t>
-        </is>
-      </c>
-      <c r="D6" s="77" t="n">
+      <c r="A6" s="55" t="inlineStr">
+        <is>
+          <t>AIRFRAME</t>
+        </is>
+      </c>
+      <c r="B6" s="56" t="n"/>
+      <c r="C6" s="56" t="n"/>
+      <c r="D6" s="56" t="n"/>
+      <c r="E6" s="56" t="n"/>
+      <c r="F6" s="56" t="n"/>
+      <c r="G6" s="56" t="n"/>
+      <c r="H6" s="56" t="n"/>
+      <c r="I6" s="56" t="n"/>
+      <c r="J6" s="56" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="33" t="n"/>
+      <c r="B7" s="79" t="inlineStr">
+        <is>
+          <t>Frame kit</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>S500 carbon-fibre quadcopter frame, 500 mm, with landing gear</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F7" s="63" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="31" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F6" s="31">
-        <f>D6*E6</f>
+      <c r="G7" s="31" t="n">
+        <v>2690</v>
+      </c>
+      <c r="H7" s="31">
+        <f>F7*G7</f>
         <v/>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="76" t="inlineStr">
+      <c r="I7" s="57" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>500 mm class. Integrated PDB in the bottom plate on most variants — check before buying a separate PDB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="55" t="inlineStr">
+        <is>
+          <t>PROPULSION</t>
+        </is>
+      </c>
+      <c r="B8" s="56" t="n"/>
+      <c r="C8" s="56" t="n"/>
+      <c r="D8" s="56" t="n"/>
+      <c r="E8" s="56" t="n"/>
+      <c r="F8" s="56" t="n"/>
+      <c r="G8" s="56" t="n"/>
+      <c r="H8" s="56" t="n"/>
+      <c r="I8" s="56" t="n"/>
+      <c r="J8" s="56" t="n"/>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="33" t="n"/>
+      <c r="B9" s="79" t="inlineStr">
         <is>
           <t>Motor</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>2216-class 900–950 KV</t>
-        </is>
-      </c>
-      <c r="D7" s="77" t="n">
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>A2212 1000 KV BLDC outrunner</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F9" s="63" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="31" t="n">
+      <c r="G9" s="31" t="n">
+        <v>1099</v>
+      </c>
+      <c r="H9" s="31">
+        <f>F9*G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="57" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>Canonical S500 pairing: A2212 1000 KV + 1045 props + 3S. Do NOT run 1000 KV on 4S with 1045 — it overspeeds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="33" t="n"/>
+      <c r="B10" s="79" t="inlineStr">
+        <is>
+          <t>ESC</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>SimonK 30 A BLDC ESC with connector</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Indian Robo Store</t>
+        </is>
+      </c>
+      <c r="E10" s="58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F10" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="31" t="n">
+        <v>336</v>
+      </c>
+      <c r="H10" s="31">
+        <f>F10*G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="57" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="inlineStr">
+        <is>
+          <t>30 A is ample for an A2212 on 3S. Flash BLHeli if you want DShot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="33" t="n"/>
+      <c r="B11" s="79" t="inlineStr">
+        <is>
+          <t>Propeller</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>1045 (10 × 4.5 in) CW + CCW pair</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>ElectronicsComp</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F11" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <v>99</v>
+      </c>
+      <c r="H11" s="31">
+        <f>F11*G11</f>
+        <v/>
+      </c>
+      <c r="I11" s="57" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Two pairs gives all four. Buy spares — these are consumables on a training aircraft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="55" t="inlineStr">
+        <is>
+          <t>AVIONICS</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="n"/>
+      <c r="C12" s="56" t="n"/>
+      <c r="D12" s="56" t="n"/>
+      <c r="E12" s="56" t="n"/>
+      <c r="F12" s="56" t="n"/>
+      <c r="G12" s="56" t="n"/>
+      <c r="H12" s="56" t="n"/>
+      <c r="I12" s="56" t="n"/>
+      <c r="J12" s="56" t="n"/>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="80" t="n"/>
+      <c r="B13" s="81" t="inlineStr">
+        <is>
+          <t>Flight controller</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Pixhawk 2.4.8, 32-bit, ArduPilot-capable</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Robokits India</t>
+        </is>
+      </c>
+      <c r="E13" s="64" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F13" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>8173</v>
+      </c>
+      <c r="H13" s="24">
+        <f>F13*G13</f>
+        <v/>
+      </c>
+      <c r="I13" s="60" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>CHOSEN FOR FIDELITY, not price. Pixhawk-standard, so it runs the same ArduPilot build and the same MAVLink as the real aircraft. Cheaper alternative: Matek F405-TE ~₹6,634 (RC Mumbai), also ArduPilot-supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="33" t="n"/>
+      <c r="B14" s="79" t="inlineStr">
+        <is>
+          <t>GNSS + compass</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>u-blox NEO-M8N with compass, for Pixhawk</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>IndiaMART (Vadodara)</t>
+        </is>
+      </c>
+      <c r="E14" s="58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F14" s="63" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="31" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H14" s="31">
+        <f>F14*G14</f>
+        <v/>
+      </c>
+      <c r="I14" s="57" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Non-RTK. Fine for a mule — the mule is not for geotag accuracy work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="82" t="n"/>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>RC receiver</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>ExpressLRS 2.4 GHz receiver (Zerodrag Nexus1 or equivalent)</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Zerodrag</t>
+        </is>
+      </c>
+      <c r="E15" s="84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F15" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H15" s="28">
+        <f>F15*G15</f>
+        <v/>
+      </c>
+      <c r="I15" s="86" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="inlineStr">
+        <is>
+          <t>Price not published. ELRS can also carry MAVLink telemetry, which may remove the separate telemetry radio below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="87" t="n"/>
+      <c r="B16" s="88" t="inlineStr">
+        <is>
+          <t>Telemetry radio</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="inlineStr">
+        <is>
+          <t>433 MHz 100 mW radio telemetry kit (air + ground)</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E16" s="66" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F16" s="89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="90" t="n">
+        <v>1560</v>
+      </c>
+      <c r="H16" s="90">
+        <f>F16*G16</f>
+        <v/>
+      </c>
+      <c r="I16" s="65" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J16" s="47" t="inlineStr">
+        <is>
+          <t>BAND CAUTION: 433 MHz kits are sold widely in India, but the delicensed SRD band is 865–867 MHz. Confirm before flying, or run telemetry over the ELRS link and delete this line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="55" t="inlineStr">
+        <is>
+          <t>POWER</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="n"/>
+      <c r="C17" s="56" t="n"/>
+      <c r="D17" s="56" t="n"/>
+      <c r="E17" s="56" t="n"/>
+      <c r="F17" s="56" t="n"/>
+      <c r="G17" s="56" t="n"/>
+      <c r="H17" s="56" t="n"/>
+      <c r="I17" s="56" t="n"/>
+      <c r="J17" s="56" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="33" t="n"/>
+      <c r="B18" s="79" t="inlineStr">
+        <is>
+          <t>Battery</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Orange / GenX 5200 mAh 3S 40C LiPo, 11.1 V</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Robocraze</t>
+        </is>
+      </c>
+      <c r="E18" s="58" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F18" s="63" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="31" t="n">
+        <v>3499</v>
+      </c>
+      <c r="H18" s="31">
+        <f>F18*G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="57" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Two packs so the mule can fly back-to-back sorties. 3S to match the 1000 KV motors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="82" t="n"/>
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>Wiring, connectors, PDB</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>XT60 leads, 14/16 AWG silicone, bullet connectors, spare PDB</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E19" s="84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F19" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>1200</v>
+      </c>
+      <c r="H19" s="28">
+        <f>F19*G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="86" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>Most S500 bottom plates integrate the PDB; this covers leads and spares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="55" t="inlineStr">
+        <is>
+          <t>PAYLOAD</t>
+        </is>
+      </c>
+      <c r="B20" s="56" t="n"/>
+      <c r="C20" s="56" t="n"/>
+      <c r="D20" s="56" t="n"/>
+      <c r="E20" s="56" t="n"/>
+      <c r="F20" s="56" t="n"/>
+      <c r="G20" s="56" t="n"/>
+      <c r="H20" s="56" t="n"/>
+      <c r="I20" s="56" t="n"/>
+      <c r="J20" s="56" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="82" t="n"/>
+      <c r="B21" s="83" t="inlineStr">
+        <is>
+          <t>Release servo</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>MG90S metal-gear micro servo + printed catch</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E21" s="84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F21" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="28" t="n">
+        <v>400</v>
+      </c>
+      <c r="H21" s="28">
+        <f>F21*G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="86" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="J21" s="27" t="inlineStr">
+        <is>
+          <t>Single station is enough to rehearse the release logic and the arming interlock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="82" t="n"/>
+      <c r="B22" s="83" t="inlineStr">
+        <is>
+          <t>Fasteners, standoffs</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>M3 nyloc, socket cap, nylon standoffs, zip ties, foam tape</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Local hardware</t>
+        </is>
+      </c>
+      <c r="E22" s="85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="28" t="n">
         <v>600</v>
       </c>
-      <c r="F7" s="31">
-        <f>D7*E7</f>
+      <c r="H22" s="28">
+        <f>F22*G22</f>
         <v/>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="B8" s="76" t="inlineStr">
-        <is>
-          <t>ESC</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>4-in-1 30 A</t>
-        </is>
-      </c>
-      <c r="D8" s="77" t="n">
+      <c r="I22" s="86" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="J22" s="27" t="inlineStr">
+        <is>
+          <t>Keep nyloc. Nothing plain on a vibrating airframe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="55" t="inlineStr">
+        <is>
+          <t>PERCEPTION</t>
+        </is>
+      </c>
+      <c r="B23" s="56" t="n"/>
+      <c r="C23" s="56" t="n"/>
+      <c r="D23" s="56" t="n"/>
+      <c r="E23" s="56" t="n"/>
+      <c r="F23" s="56" t="n"/>
+      <c r="G23" s="56" t="n"/>
+      <c r="H23" s="56" t="n"/>
+      <c r="I23" s="56" t="n"/>
+      <c r="J23" s="56" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="87" t="n"/>
+      <c r="B24" s="88" t="inlineStr">
+        <is>
+          <t>Companion computer</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="inlineStr">
+        <is>
+          <t>Raspberry Pi Zero 2 W</t>
+        </is>
+      </c>
+      <c r="D24" s="47" t="inlineStr">
+        <is>
+          <t>Robocraze</t>
+        </is>
+      </c>
+      <c r="E24" s="66" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F24" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="31" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F8" s="31">
-        <f>D8*E8</f>
+      <c r="G24" s="90" t="n">
+        <v>1950</v>
+      </c>
+      <c r="H24" s="90">
+        <f>F24*G24</f>
         <v/>
       </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="B9" s="76" t="inlineStr">
-        <is>
-          <t>Propeller</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>10 in plastic, CW/CCW</t>
-        </is>
-      </c>
-      <c r="D9" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>150</v>
-      </c>
-      <c r="F9" s="31">
-        <f>D9*E9</f>
+      <c r="I24" s="65" t="inlineStr">
+        <is>
+          <t>LISTED</t>
+        </is>
+      </c>
+      <c r="J24" s="47" t="inlineStr">
+        <is>
+          <t>STREAMING ONLY. No NPU — this cannot run the detection model and is not meant to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="82" t="n"/>
+      <c r="B25" s="83" t="inlineStr">
+        <is>
+          <t>Camera</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Raspberry Pi Camera Module 3, 12 MP</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E25" s="84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F25" s="85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H25" s="28">
+        <f>F25*G25</f>
         <v/>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="B10" s="76" t="inlineStr">
-        <is>
-          <t>Flight controller</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>F405-class, ArduPilot-capable</t>
-        </is>
-      </c>
-      <c r="D10" s="77" t="n">
+      <c r="I25" s="86" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="J25" s="27" t="inlineStr">
+        <is>
+          <t>Price not captured; confirm. Enough to exercise the video path and the GCS feed pane.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>SPARES</t>
+        </is>
+      </c>
+      <c r="B26" s="56" t="n"/>
+      <c r="C26" s="56" t="n"/>
+      <c r="D26" s="56" t="n"/>
+      <c r="E26" s="56" t="n"/>
+      <c r="F26" s="56" t="n"/>
+      <c r="G26" s="56" t="n"/>
+      <c r="H26" s="56" t="n"/>
+      <c r="I26" s="56" t="n"/>
+      <c r="J26" s="56" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="82" t="n"/>
+      <c r="B27" s="83" t="inlineStr">
+        <is>
+          <t>Test-campaign spares</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>2 spare arms, 4 spare props, 1 spare ESC, spare prop adapters</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>Robu.in</t>
+        </is>
+      </c>
+      <c r="E27" s="84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="F27" s="85" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="31" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F10" s="31">
-        <f>D10*E10</f>
+      <c r="G27" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H27" s="28">
+        <f>F27*G27</f>
         <v/>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="B11" s="76" t="inlineStr">
-        <is>
-          <t>GNSS</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>M10, non-RTK</t>
-        </is>
-      </c>
-      <c r="D11" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F11" s="31">
-        <f>D11*E11</f>
+      <c r="I27" s="86" t="inlineStr">
+        <is>
+          <t>EST</t>
+        </is>
+      </c>
+      <c r="J27" s="27" t="inlineStr">
+        <is>
+          <t>A training aircraft that cannot be repaired the same evening stops being useful.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>TOTAL, ONE MULE</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="35" t="n"/>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="36">
+        <f>SUM(H6:H27)</f>
         <v/>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="B12" s="76" t="inlineStr">
-        <is>
-          <t>Battery</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>4S 5200 mAh LiPo</t>
-        </is>
-      </c>
-      <c r="D12" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F12" s="31">
-        <f>D12*E12</f>
+      <c r="I28" s="35" t="n"/>
+      <c r="J28" s="35" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="78" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="H29" s="91" t="n">
+        <v>50000</v>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>Under budget, with headroom for spares and a second battery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="92" t="n"/>
+      <c r="B30" s="93" t="inlineStr">
+        <is>
+          <t>Three mules</t>
+        </is>
+      </c>
+      <c r="C30" s="92" t="n"/>
+      <c r="D30" s="92" t="n"/>
+      <c r="E30" s="92" t="n"/>
+      <c r="F30" s="92" t="n"/>
+      <c r="G30" s="92" t="n"/>
+      <c r="H30" s="94">
+        <f>H28*3</f>
         <v/>
       </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="76" t="inlineStr">
-        <is>
-          <t>RC receiver</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>ELRS 2.4 GHz</t>
-        </is>
-      </c>
-      <c r="D13" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="31" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F13" s="31">
-        <f>D13*E13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="B14" s="76" t="inlineStr">
-        <is>
-          <t>Telemetry radio</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>915 MHz pair</t>
-        </is>
-      </c>
-      <c r="D14" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="31" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F14" s="31">
-        <f>D14*E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="76" t="inlineStr">
-        <is>
-          <t>Camera + compute</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
-        <is>
-          <t>Pi Zero 2 W + CSI camera, streaming only</t>
-        </is>
-      </c>
-      <c r="D15" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="31" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F15" s="31">
-        <f>D15*E15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="76" t="inlineStr">
-        <is>
-          <t>Release servo</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>Single station + printed catch</t>
-        </is>
-      </c>
-      <c r="D16" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="31" t="n">
-        <v>700</v>
-      </c>
-      <c r="F16" s="31">
-        <f>D16*E16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="76" t="inlineStr">
-        <is>
-          <t>PDB, wiring, connectors</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="D17" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="31" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F17" s="31">
-        <f>D17*E17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="76" t="inlineStr">
-        <is>
-          <t>Fasteners, standoffs</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="D18" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F18" s="31">
-        <f>D18*E18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="B19" s="76" t="inlineStr">
-        <is>
-          <t>Test-campaign spares</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
-        <is>
-          <t>Props, arms, spare pack</t>
-        </is>
-      </c>
-      <c r="D19" s="77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" s="31" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F19" s="31">
-        <f>D19*E19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="34" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C20" s="35" t="n"/>
-      <c r="D20" s="35" t="n"/>
-      <c r="E20" s="35" t="n"/>
-      <c r="F20" s="36">
-        <f>SUM(F6:F19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  WHAT IT CANNOT DO — every line is a requirement failure</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="B23" s="30" t="inlineStr">
+      <c r="I30" s="92" t="n"/>
+      <c r="J30" s="95" t="inlineStr">
+        <is>
+          <t>Roughly half the cost of ONE AI compute module under Option A (₹55,000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="38" t="inlineStr">
+        <is>
+          <t>What this aircraft cannot do</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>Every line is a NIDAR requirement it fails. This is deliberate — it is a training airframe, not an entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="96" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="B34" s="96" t="inlineStr">
+        <is>
+          <t>Why it fails</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>Carry 4 × 200 g kits</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>800 g of payload on a ~1.3 kg airframe. Rule C6 fixes the kit at exactly 200 g.</t>
-        </is>
-      </c>
-      <c r="D23" s="33" t="n"/>
-      <c r="E23" s="33" t="n"/>
-      <c r="F23" s="33" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>800 g of payload on a ~1.5 kg airframe. Rule C6 fixes the kit at exactly 200 g, so it cannot be trimmed.</t>
+        </is>
+      </c>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="33" t="n"/>
+      <c r="E35" s="33" t="n"/>
+      <c r="F35" s="33" t="n"/>
+      <c r="G35" s="33" t="n"/>
+      <c r="H35" s="33" t="n"/>
+      <c r="I35" s="33" t="n"/>
+      <c r="J35" s="33" t="n"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>15 min hover endurance</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>Not at that payload fraction on a 4S 5200 pack.</t>
-        </is>
-      </c>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="33" t="n"/>
-      <c r="F24" s="33" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="B25" s="30" t="inlineStr">
-        <is>
-          <t>Recovery parachute</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Not at that payload fraction on a 3S 5200 pack.</t>
+        </is>
+      </c>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="33" t="n"/>
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="33" t="n"/>
+      <c r="J36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>Recovery parachute (SYS-41)</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>None fitted, and no mass budget to add one.</t>
         </is>
       </c>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
-      <c r="F25" s="33" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="B26" s="30" t="inlineStr">
-        <is>
-          <t>Live feed from each drone</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>A Pi Zero 2 W cannot encode three concurrent H.264 feeds in 2.5 Mbps.</t>
-        </is>
-      </c>
-      <c r="D26" s="33" t="n"/>
-      <c r="E26" s="33" t="n"/>
-      <c r="F26" s="33" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="B27" s="30" t="inlineStr">
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="33" t="n"/>
+      <c r="E37" s="33" t="n"/>
+      <c r="F37" s="33" t="n"/>
+      <c r="G37" s="33" t="n"/>
+      <c r="H37" s="33" t="n"/>
+      <c r="I37" s="33" t="n"/>
+      <c r="J37" s="33" t="n"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>Live feed from each drone (8.14)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>A Pi Zero 2 W cannot encode three concurrent H.264 feeds inside a 2.5 Mbps budget.</t>
+        </is>
+      </c>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="33" t="n"/>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="33" t="n"/>
+      <c r="J38" s="33" t="n"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>Onboard detection at 2 Hz</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>No NPU or GPU at all.</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="33" t="n"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="B28" s="30" t="inlineStr">
-        <is>
-          <t>Geotag accuracy</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Non-RTK gives ~3.1 m against ~1.3 m. About 125 of 200 points forfeited.</t>
-        </is>
-      </c>
-      <c r="D28" s="33" t="n"/>
-      <c r="E28" s="33" t="n"/>
-      <c r="F28" s="33" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>Thrust-to-weight 2.0</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Loaded, nowhere near it.</t>
-        </is>
-      </c>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="33" t="n"/>
-      <c r="F29" s="33" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>600 m range with margin</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>One 915 MHz link, no mesh, no redundant safety radio.</t>
-        </is>
-      </c>
-      <c r="D30" s="33" t="n"/>
-      <c r="E30" s="33" t="n"/>
-      <c r="F30" s="33" t="n"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  THE USEFUL VERSION OF THIS IDEA</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="14" customHeight="1">
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>This is not a competition entry. It is a good DEVELOPMENT MULE.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="14" customHeight="1">
-      <c r="B34" s="78" t="inlineStr"/>
-    </row>
-    <row r="35" ht="14" customHeight="1">
-      <c r="B35" s="78" t="inlineStr">
-        <is>
-          <t>The programme's binding constraint is an 8-week flight-test window, currently budgeted entirely on</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="14" customHeight="1">
-      <c r="B36" s="78" t="inlineStr">
-        <is>
-          <t>an aircraft that does not exist yet and cannot be risked once it does. A mule flies from week 1 and</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="B37" s="78" t="inlineStr">
-        <is>
-          <t>absorbs the work that does not need the real airframe: ground-station integration against a real</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="14" customHeight="1">
-      <c r="B38" s="78" t="inlineStr">
-        <is>
-          <t>telemetry stream, the multi-aircraft radio path with real radios, pilot currency, the 5-minute setup</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="B39" s="78" t="inlineStr">
-        <is>
-          <t>drill, failsafe behaviour on real hardware, and crash-and-rebuild practice.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="14" customHeight="1">
-      <c r="B40" s="78" t="inlineStr"/>
-    </row>
-    <row r="41" ht="14" customHeight="1">
-      <c r="B41" s="78" t="inlineStr">
-        <is>
-          <t>Three mules cost about half of one AI compute module under Option A.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="14" customHeight="1">
-      <c r="B42" s="78" t="inlineStr"/>
-    </row>
-    <row r="43" ht="14" customHeight="1">
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>RECOMMENDATION: do not pursue a ₹40,000 competition aircraft. Do consider ₹40,000 mules as</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="14" customHeight="1">
-      <c r="B44" s="78" t="inlineStr">
-        <is>
-          <t>flight-test infrastructure, funded from contingency rather than the airframe budget.</t>
-        </is>
-      </c>
-    </row>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>No NPU or GPU. The §8.2 tiling budget is unreachable by orders of magnitude.</t>
+        </is>
+      </c>
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="33" t="n"/>
+      <c r="E39" s="33" t="n"/>
+      <c r="F39" s="33" t="n"/>
+      <c r="G39" s="33" t="n"/>
+      <c r="H39" s="33" t="n"/>
+      <c r="I39" s="33" t="n"/>
+      <c r="J39" s="33" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>Geotag accuracy (200 pts)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Non-RTK M8N gives ~3.1 m against ~1.3 m. About 125 of 200 points forfeited.</t>
+        </is>
+      </c>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="33" t="n"/>
+      <c r="E40" s="33" t="n"/>
+      <c r="F40" s="33" t="n"/>
+      <c r="G40" s="33" t="n"/>
+      <c r="H40" s="33" t="n"/>
+      <c r="I40" s="33" t="n"/>
+      <c r="J40" s="33" t="n"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>Thrust-to-weight 2.0 at MTOW</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Achieves it empty; nowhere near it loaded.</t>
+        </is>
+      </c>
+      <c r="C41" s="33" t="n"/>
+      <c r="D41" s="33" t="n"/>
+      <c r="E41" s="33" t="n"/>
+      <c r="F41" s="33" t="n"/>
+      <c r="G41" s="33" t="n"/>
+      <c r="H41" s="33" t="n"/>
+      <c r="I41" s="33" t="n"/>
+      <c r="J41" s="33" t="n"/>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>600 m range with link margin</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>One low-power telemetry link, no mesh, no redundant safety radio.</t>
+        </is>
+      </c>
+      <c r="C42" s="33" t="n"/>
+      <c r="D42" s="33" t="n"/>
+      <c r="E42" s="33" t="n"/>
+      <c r="F42" s="33" t="n"/>
+      <c r="G42" s="33" t="n"/>
+      <c r="H42" s="33" t="n"/>
+      <c r="I42" s="33" t="n"/>
+      <c r="J42" s="33" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="38" t="inlineStr">
+        <is>
+          <t>What it IS for</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="20" t="inlineStr">
+        <is>
+          <t>•  Ground-station integration: mission file parsed, partitioned and rendered against a real MAVLink stream, not SITL loopback.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="20" t="inlineStr">
+        <is>
+          <t>•  The multi-aircraft radio path with real radios — the failure mode that made the ingest read zeros for weeks was invisible in simulation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>•  Pilot currency, launch and recovery procedure, and the 5-minute setup drill. SYS-21 is still MODELLED, NOT MEASURED, and is the highest-priority test in the programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="20" t="inlineStr">
+        <is>
+          <t>•  Failsafe behaviour on real hardware, where a wrong parameter costs a ₹37,000 airframe instead of a ₹2.6 L one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="20" t="inlineStr">
+        <is>
+          <t>•  Crash-and-rebuild practice, which is what the spares line exists to survive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="97" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION: fund from contingency, not from the airframe budget. The question was whether a drone under ₹50,000 is possible — it is, and it is worth building, but it is flight-test infrastructure rather than a cheaper competition aircraft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52"/>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="B43:F43"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B42:F42"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B35:F35"/>
+  <mergeCells count="18">
+    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="B37:J37"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B40:J40"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="A51:J52"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="B38:J38"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A49:J49"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
     <oddFooter>&amp;LRescueSwarm Cost Study rev D · 2026-08-11&amp;R&amp;P / &amp;N</oddFooter>

--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,8 +178,13 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -726,96 +731,112 @@
     <row r="15" ht="16" customHeight="1">
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Duty and freight</t>
+          <t>Tax-inclusive retail</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>92698</v>
+        <v>466000</v>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>22% on the imported residual</t>
+          <t>Dated Indian listings. No tax added.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>GST</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>134272</v>
-      </c>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="14" t="inlineStr">
-        <is>
-          <t>18%</t>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Ex-GST quotes and services</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>182260</v>
+      </c>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Quotes and fabrication. Taxed.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Contingency</t>
+          <t>Duty and freight</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>132034</v>
+        <v>25863</v>
       </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>15% - phased release is itself a reserve</t>
+          <t>22%, ex-tax lines only</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>TOTAL ASK</t>
+          <t>GST</t>
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1012264</v>
+        <v>37462</v>
       </c>
       <c r="D18" s="13" t="n"/>
       <c r="E18" s="14" t="inlineStr">
         <is>
-          <t>10.12 lakh</t>
+          <t>18%, ex-tax lines only</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Institutional contribution</t>
+          <t>Contingency</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>354000</v>
+        <v>107488</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10" t="inlineStr">
         <is>
+          <t>15% - phased release is itself a reserve</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL ASK</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="n">
+        <v>824072</v>
+      </c>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>8.24 lakh</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Institutional contribution</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>354000</v>
+      </c>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
           <t>Equipment already held - co-funding in kind</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Indigenous content</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="10" t="inlineStr">
-        <is>
-          <t>Computed from per-line fractions, not estimated</t>
         </is>
       </c>
     </row>
@@ -825,34 +846,44 @@
           <t xml:space="preserve">  WHAT THIS CONFIGURATION GIVES UP</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>Indigenous content</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Computed from per-line fractions, not estimated</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>- Nothing that is scored. RTK geolocation, onboard detection at rate, three concurrent video feeds and four-station delivery all survive.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>- Margin: published thrust data, supplier support, spares depth.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>- Indigenous content, 58% -&gt; 36%. The imported autopilot and generic propulsion are what make it affordable and what make it less Indian.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>- Restoring the Indian autopilot and propulsion costs about 1.39 L across the fleet.</t>
         </is>
@@ -870,21 +901,21 @@
       <c r="E28" s="5" t="n"/>
     </row>
     <row r="29" ht="40" customHeight="1">
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>1.  INSURANCE was deferred at team direction. Third-party cover is commonly mandatory for Indian UAV operations. Confirm before any flight.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="40" customHeight="1">
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>2.  DUTY AND GST MAY BE DOUBLE-COUNTED. The model adds 22% duty and 18% GST on top of prices that are largely Indian retail listings, already duty- and tax-paid. Exposure is roughly 2.3 L. A per-line audit is the largest remaining correction and it is an accounting fix, not a capability cut.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="40" customHeight="1">
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>3.  MOTOR THRUST is unverified. The selected motors publish no thrust curve; the stand characterises them in P5, and a shortfall then forces a propulsion change.</t>
         </is>
@@ -946,136 +977,136 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Unit INR</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Ext INR</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Why this grade</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Flight controller</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="24" t="n">
         <v>22600</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="24">
         <f>C5*D5</f>
         <v/>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Holybro Pixhawk 6C Mini. Dual IMU, Pixhawk standard, ArduPilot native.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="B6" s="19" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>AI accelerator</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="24" t="n">
         <v>20000</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="24">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>26 TOPS. The specification floor, not a preference.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>GNSS RTK primary</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="24" t="n">
         <v>18000</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="24">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>No cheaper RTK-capable part exists. Governs 125 of 200 geotag points.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Motors</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="29" t="n">
         <v>4500</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="29">
         <f>C8*D8</f>
         <v/>
       </c>
@@ -1086,150 +1117,150 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="B9" s="19" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Li-ion cells</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="24" t="n">
         <v>700</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="24">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>Capacity- and IR-matched. One weak cell defines the whole pack.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="B10" s="19" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>Structure</t>
         </is>
       </c>
-      <c r="C10" s="20" t="n">
+      <c r="C10" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="21" t="n">
+      <c r="D10" s="24" t="n">
         <v>13000</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="24">
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>In-house fabrication; institute machine shop confirmed.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>Camera + lens</t>
         </is>
       </c>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="24" t="n">
         <v>11100</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="24">
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Arducam IMX477 + 6 mm. Pi-compatible; GSD drives detection.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Pack, BMS, PDB, BEC</t>
         </is>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="29" t="n">
         <v>8500</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="29">
         <f>C12*D12</f>
         <v/>
       </c>
       <c r="F12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>RC rx, storage, cooling, mounts</t>
         </is>
       </c>
-      <c r="C13" s="25" t="n">
+      <c r="C13" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="29" t="n">
         <v>8500</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="29">
         <f>C13*D13</f>
         <v/>
       </c>
       <c r="F13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>ESCs</t>
         </is>
       </c>
-      <c r="C14" s="25" t="n">
+      <c r="C14" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="29" t="n">
         <v>1800</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="29">
         <f>C14*D14</f>
         <v/>
       </c>
@@ -1240,23 +1271,23 @@
       </c>
     </row>
     <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Mesh node + antennas</t>
         </is>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="29" t="n">
         <v>6000</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="29">
         <f>C15*D15</f>
         <v/>
       </c>
@@ -1267,23 +1298,23 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Payload system</t>
         </is>
       </c>
-      <c r="C16" s="25" t="n">
+      <c r="C16" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="29" t="n">
         <v>4500</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="29">
         <f>C16*D16</f>
         <v/>
       </c>
@@ -1294,23 +1325,23 @@
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="23" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Propellers</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n">
+      <c r="C17" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="29" t="n">
         <v>1000</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="29">
         <f>C17*D17</f>
         <v/>
       </c>
@@ -1321,80 +1352,80 @@
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Wiring, connectors</t>
         </is>
       </c>
-      <c r="C18" s="25" t="n">
+      <c r="C18" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="29" t="n">
         <v>2400</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="29">
         <f>C18*D18</f>
         <v/>
       </c>
       <c r="F18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="26" t="inlineStr">
         <is>
           <t>hobby</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Prop adapters</t>
         </is>
       </c>
-      <c r="C19" s="25" t="n">
+      <c r="C19" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="29" t="n">
         <v>350</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="29">
         <f>C19*D19</f>
         <v/>
       </c>
       <c r="F19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n"/>
-      <c r="B20" s="28" t="inlineStr">
+      <c r="A20" s="30" t="n"/>
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>TOTAL PER AIRCRAFT</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="29">
+      <c r="C20" s="30" t="n"/>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="32">
         <f>SUM(E5:E19)</f>
         <v/>
       </c>
-      <c r="F20" s="27" t="n"/>
+      <c r="F20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="27" t="n"/>
-      <c r="B21" s="28" t="inlineStr">
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="31" t="inlineStr">
         <is>
           <t>x3 FLEET</t>
         </is>
       </c>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="29">
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="32">
         <f>E20*3</f>
         <v/>
       </c>
-      <c r="F21" s="27" t="n"/>
+      <c r="F21" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1442,63 +1473,63 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Original</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Ask</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>Delta</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>Air vehicle and payload</t>
         </is>
       </c>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="31" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="31" t="n"/>
+      <c r="B5" s="34" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="9" t="n"/>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>Air vehicles, 3 x 157,800</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="29" t="n">
         <v>790203</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="29" t="n">
         <v>473400</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="35" t="n">
         <v>-316803</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
@@ -1509,18 +1540,18 @@
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="9" t="n"/>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Relief kits (14)</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="29" t="n">
         <v>5600</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="29" t="n">
         <v>5600</v>
       </c>
-      <c r="E7" s="32" t="n">
+      <c r="E7" s="35" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="10" t="inlineStr">
@@ -1531,18 +1562,18 @@
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="n"/>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Ground-truth apparatus</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="29" t="n">
         <v>35280</v>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="29" t="n">
         <v>4860</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="35" t="n">
         <v>-30420</v>
       </c>
       <c r="F8" s="10" t="inlineStr">
@@ -1552,100 +1583,100 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="33" t="n"/>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="A9" s="36" t="n"/>
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>Recovery parachutes, 3</t>
         </is>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="36" t="n">
+      <c r="E9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. PERMITTED, not required (rulebook-compliance 6.2). A crash is -50 against -10 for landing outside the zone: a ~40-point bet.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>Ground segment</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n"/>
-      <c r="C10" s="31" t="n"/>
-      <c r="D10" s="31" t="n"/>
-      <c r="E10" s="31" t="n"/>
-      <c r="F10" s="31" t="n"/>
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n"/>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="38" t="n"/>
-      <c r="B11" s="19" t="inlineStr">
+      <c r="A11" s="41" t="n"/>
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>GCS laptop</t>
         </is>
       </c>
-      <c r="C11" s="21" t="n">
+      <c r="C11" s="24" t="n">
         <v>85000</v>
       </c>
-      <c r="D11" s="21" t="n">
+      <c r="D11" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="39" t="n">
+      <c r="E11" s="42" t="n">
         <v>-85000</v>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>R1: team-supplied.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="38" t="n"/>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="A12" s="41" t="n"/>
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>Backup GCS laptop</t>
         </is>
       </c>
-      <c r="C12" s="21" t="n">
+      <c r="C12" s="24" t="n">
         <v>55000</v>
       </c>
-      <c r="D12" s="21" t="n">
+      <c r="D12" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="39" t="n">
+      <c r="E12" s="42" t="n">
         <v>-55000</v>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>R1: team-supplied.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="38" t="n"/>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="A13" s="41" t="n"/>
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>Portable power station</t>
         </is>
       </c>
-      <c r="C13" s="21" t="n">
+      <c r="C13" s="24" t="n">
         <v>55000</v>
       </c>
-      <c r="D13" s="21" t="n">
+      <c r="D13" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="39" t="n">
+      <c r="E13" s="42" t="n">
         <v>-55000</v>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>R1: institute field power.</t>
         </is>
@@ -1653,18 +1684,18 @@
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="9" t="n"/>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>RTK base receiver</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n">
+      <c r="C14" s="29" t="n">
         <v>38000</v>
       </c>
-      <c r="D14" s="26" t="n">
+      <c r="D14" s="29" t="n">
         <v>18000</v>
       </c>
-      <c r="E14" s="32" t="n">
+      <c r="E14" s="35" t="n">
         <v>-20000</v>
       </c>
       <c r="F14" s="10" t="inlineStr">
@@ -1675,18 +1706,18 @@
     </row>
     <row r="15" ht="26" customHeight="1">
       <c r="A15" s="9" t="n"/>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Survey tripod + tribrach</t>
         </is>
       </c>
-      <c r="C15" s="26" t="n">
+      <c r="C15" s="29" t="n">
         <v>9500</v>
       </c>
-      <c r="D15" s="26" t="n">
+      <c r="D15" s="29" t="n">
         <v>4000</v>
       </c>
-      <c r="E15" s="32" t="n">
+      <c r="E15" s="35" t="n">
         <v>-5500</v>
       </c>
       <c r="F15" s="10" t="inlineStr">
@@ -1697,18 +1728,18 @@
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="9" t="n"/>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Equipment cases</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="29" t="n">
         <v>44000</v>
       </c>
-      <c r="D16" s="26" t="n">
+      <c r="D16" s="29" t="n">
         <v>9000</v>
       </c>
-      <c r="E16" s="32" t="n">
+      <c r="E16" s="35" t="n">
         <v>-35000</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
@@ -1719,18 +1750,18 @@
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="9" t="n"/>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Fire extinguisher, sand, charging bags</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="29" t="n">
         <v>11000</v>
       </c>
-      <c r="D17" s="26" t="n">
+      <c r="D17" s="29" t="n">
         <v>4000</v>
       </c>
-      <c r="E17" s="32" t="n">
+      <c r="E17" s="35" t="n">
         <v>-7000</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
@@ -1741,18 +1772,18 @@
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="9" t="n"/>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Safety-pilot transmitter</t>
         </is>
       </c>
-      <c r="C18" s="26" t="n">
+      <c r="C18" s="29" t="n">
         <v>16000</v>
       </c>
-      <c r="D18" s="26" t="n">
+      <c r="D18" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="E18" s="32" t="n">
+      <c r="E18" s="35" t="n">
         <v>-8000</v>
       </c>
       <c r="F18" s="10" t="inlineStr">
@@ -1763,18 +1794,18 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="9" t="n"/>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Sun hood + observer monitor</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="29" t="n">
         <v>12000</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="29" t="n">
         <v>1500</v>
       </c>
-      <c r="E19" s="32" t="n">
+      <c r="E19" s="35" t="n">
         <v>-10500</v>
       </c>
       <c r="F19" s="10" t="inlineStr">
@@ -1785,18 +1816,18 @@
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="9" t="n"/>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Remaining ground items</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="29" t="n">
         <v>62800</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="29" t="n">
         <v>25000</v>
       </c>
-      <c r="E20" s="32" t="n">
+      <c r="E20" s="35" t="n">
         <v>-37800</v>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -1806,34 +1837,34 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>Test equipment</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="31" t="n"/>
-      <c r="D21" s="31" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="31" t="n"/>
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="34" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="38" t="n"/>
-      <c r="B22" s="19" t="inlineStr">
+      <c r="A22" s="41" t="n"/>
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>3D printer</t>
         </is>
       </c>
-      <c r="C22" s="21" t="n">
+      <c r="C22" s="24" t="n">
         <v>50000</v>
       </c>
-      <c r="D22" s="21" t="n">
+      <c r="D22" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E22" s="39" t="n">
+      <c r="E22" s="42" t="n">
         <v>-50000</v>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>R1: department facility.</t>
         </is>
@@ -1841,18 +1872,18 @@
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="9" t="n"/>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>Thrust stand</t>
         </is>
       </c>
-      <c r="C23" s="26" t="n">
+      <c r="C23" s="29" t="n">
         <v>45000</v>
       </c>
-      <c r="D23" s="26" t="n">
+      <c r="D23" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="E23" s="32" t="n">
+      <c r="E23" s="35" t="n">
         <v>-37000</v>
       </c>
       <c r="F23" s="10" t="inlineStr">
@@ -1863,18 +1894,18 @@
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="24" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>Battery chargers</t>
         </is>
       </c>
-      <c r="C24" s="26" t="n">
+      <c r="C24" s="29" t="n">
         <v>28000</v>
       </c>
-      <c r="D24" s="26" t="n">
+      <c r="D24" s="29" t="n">
         <v>14000</v>
       </c>
-      <c r="E24" s="32" t="n">
+      <c r="E24" s="35" t="n">
         <v>-14000</v>
       </c>
       <c r="F24" s="10" t="inlineStr">
@@ -1884,110 +1915,110 @@
       </c>
     </row>
     <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="33" t="n"/>
-      <c r="B25" s="34" t="inlineStr">
+      <c r="A25" s="36" t="n"/>
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>Cell tester</t>
         </is>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="38" t="n">
         <v>13000</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E25" s="36" t="n">
+      <c r="E25" s="39" t="n">
         <v>-13000</v>
       </c>
-      <c r="F25" s="37" t="inlineStr">
+      <c r="F25" s="40" t="inlineStr">
         <is>
           <t>Most 1C chargers measure per-cell IR. CONFIRM before deleting.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="38" t="n"/>
-      <c r="B26" s="19" t="inlineStr">
+      <c r="A26" s="41" t="n"/>
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>Soldering station</t>
         </is>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="24" t="n">
         <v>9000</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="39" t="n">
+      <c r="E26" s="42" t="n">
         <v>-9000</v>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t>R1: department facility.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="38" t="n"/>
-      <c r="B27" s="19" t="inlineStr">
+      <c r="A27" s="41" t="n"/>
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>Rotary tool + CF extraction</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="24" t="n">
         <v>8500</v>
       </c>
-      <c r="D27" s="21" t="n">
+      <c r="D27" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E27" s="39" t="n">
+      <c r="E27" s="42" t="n">
         <v>-8500</v>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="25" t="inlineStr">
         <is>
           <t>R1: department facility.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="38" t="n"/>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="A28" s="41" t="n"/>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>Bench power supply</t>
         </is>
       </c>
-      <c r="C28" s="21" t="n">
+      <c r="C28" s="24" t="n">
         <v>8500</v>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E28" s="39" t="n">
+      <c r="E28" s="42" t="n">
         <v>-8500</v>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>R1: department facility.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="38" t="n"/>
-      <c r="B29" s="19" t="inlineStr">
+      <c r="A29" s="41" t="n"/>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>Multimeters</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="D29" s="21" t="n">
+      <c r="D29" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E29" s="39" t="n">
+      <c r="E29" s="42" t="n">
         <v>-8000</v>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>R1: department facility.</t>
         </is>
@@ -1995,18 +2026,18 @@
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="9" t="n"/>
-      <c r="B30" s="24" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Charger PSU</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n">
+      <c r="C30" s="29" t="n">
         <v>8000</v>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="29" t="n">
         <v>1500</v>
       </c>
-      <c r="E30" s="32" t="n">
+      <c r="E30" s="35" t="n">
         <v>-6500</v>
       </c>
       <c r="F30" s="10" t="inlineStr">
@@ -2017,18 +2048,18 @@
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="9" t="n"/>
-      <c r="B31" s="24" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Calibrated scale + remaining</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n">
+      <c r="C31" s="29" t="n">
         <v>47700</v>
       </c>
-      <c r="D31" s="26" t="n">
+      <c r="D31" s="29" t="n">
         <v>12000</v>
       </c>
-      <c r="E31" s="32" t="n">
+      <c r="E31" s="35" t="n">
         <v>-35700</v>
       </c>
       <c r="F31" s="10" t="inlineStr">
@@ -2038,31 +2069,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>Spares and consumables</t>
         </is>
       </c>
-      <c r="B32" s="31" t="n"/>
-      <c r="C32" s="31" t="n"/>
-      <c r="D32" s="31" t="n"/>
-      <c r="E32" s="31" t="n"/>
-      <c r="F32" s="31" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="34" t="n"/>
+      <c r="D32" s="34" t="n"/>
+      <c r="E32" s="34" t="n"/>
+      <c r="F32" s="34" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="9" t="n"/>
-      <c r="B33" s="24" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>Spare airframe structure set</t>
         </is>
       </c>
-      <c r="C33" s="26" t="n">
+      <c r="C33" s="29" t="n">
         <v>25000</v>
       </c>
-      <c r="D33" s="26" t="n">
+      <c r="D33" s="29" t="n">
         <v>25000</v>
       </c>
-      <c r="E33" s="32" t="n">
+      <c r="E33" s="35" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="10" t="inlineStr">
@@ -2073,18 +2104,18 @@
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="9" t="n"/>
-      <c r="B34" s="24" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>Spare propellers, plate and tube stock</t>
         </is>
       </c>
-      <c r="C34" s="26" t="n">
+      <c r="C34" s="29" t="n">
         <v>26200</v>
       </c>
-      <c r="D34" s="26" t="n">
+      <c r="D34" s="29" t="n">
         <v>21400</v>
       </c>
-      <c r="E34" s="32" t="n">
+      <c r="E34" s="35" t="n">
         <v>-4800</v>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -2095,18 +2126,18 @@
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="9" t="n"/>
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>Fasteners, tape, connectors, filament</t>
         </is>
       </c>
-      <c r="C35" s="26" t="n">
+      <c r="C35" s="29" t="n">
         <v>37800</v>
       </c>
-      <c r="D35" s="26" t="n">
+      <c r="D35" s="29" t="n">
         <v>13000</v>
       </c>
-      <c r="E35" s="32" t="n">
+      <c r="E35" s="35" t="n">
         <v>-24800</v>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -2116,232 +2147,232 @@
       </c>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="33" t="n"/>
-      <c r="B36" s="34" t="inlineStr">
+      <c r="A36" s="36" t="n"/>
+      <c r="B36" s="37" t="inlineStr">
         <is>
           <t>Spare battery packs</t>
         </is>
       </c>
-      <c r="C36" s="35" t="n">
+      <c r="C36" s="38" t="n">
         <v>57000</v>
       </c>
-      <c r="D36" s="35" t="n">
+      <c r="D36" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="36" t="n">
+      <c r="E36" s="39" t="n">
         <v>-57000</v>
       </c>
-      <c r="F36" s="37" t="inlineStr">
+      <c r="F36" s="40" t="inlineStr">
         <is>
           <t>DEFERRED.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="33" t="n"/>
-      <c r="B37" s="34" t="inlineStr">
+      <c r="A37" s="36" t="n"/>
+      <c r="B37" s="37" t="inlineStr">
         <is>
           <t>Spare motors</t>
         </is>
       </c>
-      <c r="C37" s="35" t="n">
+      <c r="C37" s="38" t="n">
         <v>28000</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="36" t="n">
+      <c r="E37" s="39" t="n">
         <v>-28000</v>
       </c>
-      <c r="F37" s="37" t="inlineStr">
+      <c r="F37" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. 2-3 week domestic lead time is the mitigation.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="33" t="n"/>
-      <c r="B38" s="34" t="inlineStr">
+      <c r="A38" s="36" t="n"/>
+      <c r="B38" s="37" t="inlineStr">
         <is>
           <t>Spare compute module</t>
         </is>
       </c>
-      <c r="C38" s="35" t="n">
+      <c r="C38" s="38" t="n">
         <v>38000</v>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="36" t="n">
+      <c r="E38" s="39" t="n">
         <v>-38000</v>
       </c>
-      <c r="F38" s="37" t="inlineStr">
+      <c r="F38" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. Accepted risk.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="33" t="n"/>
-      <c r="B39" s="34" t="inlineStr">
+      <c r="A39" s="36" t="n"/>
+      <c r="B39" s="37" t="inlineStr">
         <is>
           <t>Spare flight controller</t>
         </is>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="38" t="n">
         <v>26000</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="36" t="n">
+      <c r="E39" s="39" t="n">
         <v>-26000</v>
       </c>
-      <c r="F39" s="37" t="inlineStr">
+      <c r="F39" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. Accepted risk.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="33" t="n"/>
-      <c r="B40" s="34" t="inlineStr">
+      <c r="A40" s="36" t="n"/>
+      <c r="B40" s="37" t="inlineStr">
         <is>
           <t>Spare GNSS</t>
         </is>
       </c>
-      <c r="C40" s="35" t="n">
+      <c r="C40" s="38" t="n">
         <v>18000</v>
       </c>
-      <c r="D40" s="35" t="n">
+      <c r="D40" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="36" t="n">
+      <c r="E40" s="39" t="n">
         <v>-18000</v>
       </c>
-      <c r="F40" s="37" t="inlineStr">
+      <c r="F40" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. Accepted risk.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="33" t="n"/>
-      <c r="B41" s="34" t="inlineStr">
+      <c r="A41" s="36" t="n"/>
+      <c r="B41" s="37" t="inlineStr">
         <is>
           <t>Spare camera + lens</t>
         </is>
       </c>
-      <c r="C41" s="35" t="n">
+      <c r="C41" s="38" t="n">
         <v>16600</v>
       </c>
-      <c r="D41" s="35" t="n">
+      <c r="D41" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="36" t="n">
+      <c r="E41" s="39" t="n">
         <v>-16600</v>
       </c>
-      <c r="F41" s="37" t="inlineStr">
+      <c r="F41" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. Accepted risk.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="33" t="inlineStr">
         <is>
           <t>Software, data and regulatory</t>
         </is>
       </c>
-      <c r="B42" s="31" t="n"/>
-      <c r="C42" s="31" t="n"/>
-      <c r="D42" s="31" t="n"/>
-      <c r="E42" s="31" t="n"/>
-      <c r="F42" s="31" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="D42" s="34" t="n"/>
+      <c r="E42" s="34" t="n"/>
+      <c r="F42" s="34" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="38" t="n"/>
-      <c r="B43" s="19" t="inlineStr">
+      <c r="A43" s="41" t="n"/>
+      <c r="B43" s="22" t="inlineStr">
         <is>
           <t>Training compute</t>
         </is>
       </c>
-      <c r="C43" s="21" t="n">
+      <c r="C43" s="24" t="n">
         <v>75000</v>
       </c>
-      <c r="D43" s="21" t="n">
+      <c r="D43" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="39" t="n">
+      <c r="E43" s="42" t="n">
         <v>-75000</v>
       </c>
-      <c r="F43" s="22" t="inlineStr">
+      <c r="F43" s="25" t="inlineStr">
         <is>
           <t>R1: institute GPUs.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="33" t="n"/>
-      <c r="B44" s="34" t="inlineStr">
+      <c r="A44" s="36" t="n"/>
+      <c r="B44" s="37" t="inlineStr">
         <is>
           <t>Indian SAR field dataset</t>
         </is>
       </c>
-      <c r="C44" s="35" t="n">
+      <c r="C44" s="38" t="n">
         <v>60000</v>
       </c>
-      <c r="D44" s="35" t="n">
+      <c r="D44" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="36" t="n">
+      <c r="E44" s="39" t="n">
         <v>-60000</v>
       </c>
-      <c r="F44" s="37" t="inlineStr">
+      <c r="F44" s="40" t="inlineStr">
         <is>
           <t>DEFERRED. Detection recall stays MODELLED.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="33" t="n"/>
-      <c r="B45" s="34" t="inlineStr">
+      <c r="A45" s="36" t="n"/>
+      <c r="B45" s="37" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="C45" s="35" t="n">
+      <c r="C45" s="38" t="n">
         <v>25000</v>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="36" t="n">
+      <c r="E45" s="39" t="n">
         <v>-25000</v>
       </c>
-      <c r="F45" s="37" t="inlineStr">
+      <c r="F45" s="40" t="inlineStr">
         <is>
           <t>DEFERRED AT TEAM DIRECTION. MUST BE CONFIRMED against the rulebook and DGCA rules before any flight.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="33" t="n"/>
-      <c r="B46" s="34" t="inlineStr">
+      <c r="A46" s="36" t="n"/>
+      <c r="B46" s="37" t="inlineStr">
         <is>
           <t>WPC / ETA licensing</t>
         </is>
       </c>
-      <c r="C46" s="35" t="n">
+      <c r="C46" s="38" t="n">
         <v>10000</v>
       </c>
-      <c r="D46" s="35" t="n">
+      <c r="D46" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="36" t="n">
+      <c r="E46" s="39" t="n">
         <v>-10000</v>
       </c>
-      <c r="F46" s="37" t="inlineStr">
+      <c r="F46" s="40" t="inlineStr">
         <is>
           <t>REMOVED. Every link is delicensed: 2.4/5.8 GHz ISM and 865-867 MHz SRD. Type approval is a supplier obligation.</t>
         </is>
@@ -2349,18 +2380,18 @@
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="9" t="n"/>
-      <c r="B47" s="24" t="inlineStr">
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>DGCA registration</t>
         </is>
       </c>
-      <c r="C47" s="26" t="n">
+      <c r="C47" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="D47" s="26" t="n">
+      <c r="D47" s="29" t="n">
         <v>5000</v>
       </c>
-      <c r="E47" s="32" t="n">
+      <c r="E47" s="35" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="10" t="inlineStr">
@@ -2370,74 +2401,74 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="27" t="n"/>
-      <c r="B48" s="28" t="inlineStr">
+      <c r="A48" s="30" t="n"/>
+      <c r="B48" s="31" t="inlineStr">
         <is>
           <t>SUBTOTAL</t>
         </is>
       </c>
-      <c r="C48" s="27" t="n"/>
-      <c r="D48" s="29" t="n">
+      <c r="C48" s="30" t="n"/>
+      <c r="D48" s="32" t="n">
         <v>653260</v>
       </c>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="27" t="n"/>
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="27" t="n"/>
-      <c r="B49" s="28" t="inlineStr">
+      <c r="A49" s="30" t="n"/>
+      <c r="B49" s="31" t="inlineStr">
         <is>
           <t>Duty and freight</t>
         </is>
       </c>
-      <c r="C49" s="27" t="n"/>
-      <c r="D49" s="29" t="n">
-        <v>92698</v>
-      </c>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="27" t="n"/>
+      <c r="C49" s="30" t="n"/>
+      <c r="D49" s="32" t="n">
+        <v>25863</v>
+      </c>
+      <c r="E49" s="30" t="n"/>
+      <c r="F49" s="30" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="27" t="n"/>
-      <c r="B50" s="28" t="inlineStr">
+      <c r="A50" s="30" t="n"/>
+      <c r="B50" s="31" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="C50" s="27" t="n"/>
-      <c r="D50" s="29" t="n">
-        <v>134272</v>
-      </c>
-      <c r="E50" s="27" t="n"/>
-      <c r="F50" s="27" t="n"/>
+      <c r="C50" s="30" t="n"/>
+      <c r="D50" s="32" t="n">
+        <v>37462</v>
+      </c>
+      <c r="E50" s="30" t="n"/>
+      <c r="F50" s="30" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="27" t="n"/>
-      <c r="B51" s="28" t="inlineStr">
+      <c r="A51" s="30" t="n"/>
+      <c r="B51" s="31" t="inlineStr">
         <is>
           <t>Contingency</t>
         </is>
       </c>
-      <c r="C51" s="27" t="n"/>
-      <c r="D51" s="29" t="n">
-        <v>132034</v>
-      </c>
-      <c r="E51" s="27" t="n"/>
-      <c r="F51" s="27" t="n"/>
+      <c r="C51" s="30" t="n"/>
+      <c r="D51" s="32" t="n">
+        <v>107488</v>
+      </c>
+      <c r="E51" s="30" t="n"/>
+      <c r="F51" s="30" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="27" t="n"/>
-      <c r="B52" s="28" t="inlineStr">
+      <c r="A52" s="30" t="n"/>
+      <c r="B52" s="31" t="inlineStr">
         <is>
           <t>TOTAL ASK</t>
         </is>
       </c>
-      <c r="C52" s="27" t="n"/>
-      <c r="D52" s="29" t="n">
-        <v>1012264</v>
-      </c>
-      <c r="E52" s="27" t="n"/>
-      <c r="F52" s="27" t="n"/>
+      <c r="C52" s="30" t="n"/>
+      <c r="D52" s="32" t="n">
+        <v>824072</v>
+      </c>
+      <c r="E52" s="30" t="n"/>
+      <c r="F52" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -2483,37 +2514,37 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>What it buys back</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="40" t="n">
+      <c r="A5" s="43" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="41" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Flight insurance</t>
         </is>
       </c>
-      <c r="C5" s="42" t="n">
+      <c r="C5" s="45" t="n">
         <v>25000</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -2523,15 +2554,15 @@
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="40" t="n">
+      <c r="A6" s="43" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="41" t="inlineStr">
+      <c r="B6" s="44" t="inlineStr">
         <is>
           <t>Second GNSS receiver (3)</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="45" t="n">
         <v>51000</v>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -2541,15 +2572,15 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="n">
+      <c r="A7" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Recovery parachutes (3)</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="29" t="n">
         <v>36000</v>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -2559,15 +2590,15 @@
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Training airframe</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="29" t="n">
         <v>37309</v>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -2577,15 +2608,15 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Sub-GHz safety radio (3)</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="29" t="n">
         <v>58065</v>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -2595,15 +2626,15 @@
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="28" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Spare packs and motors</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="29" t="n">
         <v>74396</v>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -2613,15 +2644,15 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="28" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Field data campaign</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="29" t="n">
         <v>15000</v>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -2631,15 +2662,15 @@
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Spare compute module</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="29" t="n">
         <v>20000</v>
       </c>
       <c r="D12" s="10" t="inlineStr">
@@ -2649,16 +2680,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="28" t="inlineStr">
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="31" t="inlineStr">
         <is>
           <t>TOTAL DEFERRED</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="32" t="n">
         <v>316770</v>
       </c>
-      <c r="D13" s="27" t="n"/>
+      <c r="D13" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -2705,34 +2736,34 @@
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="17" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>Part</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="20" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="20" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="E4" s="17" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>INR</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Flight controller</t>
         </is>
@@ -2747,92 +2778,92 @@
           <t>Indian Robo Store</t>
         </is>
       </c>
-      <c r="D5" s="44" t="inlineStr">
+      <c r="D5" s="47" t="inlineStr">
         <is>
           <t>https://www.indiamart.com/proddetail/pixhawk-6c-mini-flight-controller-2852778303248.html</t>
         </is>
       </c>
-      <c r="E5" s="45" t="n">
+      <c r="E5" s="48" t="n">
         <v>22600</v>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Flight controller (deferred)</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>Agam Autopilot V6X-RT Full Set</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="40" t="inlineStr">
         <is>
           <t>Agam Robotics</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>https://www.agamrobotics.com/product-page/agam-pixhawk-6x-full-set</t>
         </is>
       </c>
-      <c r="E6" s="48" t="n">
+      <c r="E6" s="51" t="n">
         <v>42000</v>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="46" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>Motor (deferred)</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="40" t="inlineStr">
         <is>
           <t>Reflex Drive RD MI-5008 KV340</t>
         </is>
       </c>
-      <c r="C7" s="37" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>Reflex Drive, Lucknow</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>https://reflexdrive.in/product/rd-mi-5008-motor/</t>
         </is>
       </c>
-      <c r="E7" s="48" t="n">
+      <c r="E7" s="51" t="n">
         <v>9099</v>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="46" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>ESC (deferred)</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="40" t="inlineStr">
         <is>
           <t>Reflex Drive RD A-Series FOC 60 A</t>
         </is>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="40" t="inlineStr">
         <is>
           <t>Reflex Drive</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>https://reflexdrive.in/product/rd-a-series-foc-esc-60a/</t>
         </is>
       </c>
-      <c r="E8" s="48" t="n">
+      <c r="E8" s="51" t="n">
         <v>3400</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="43" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Li-ion cell</t>
         </is>
@@ -2847,17 +2878,17 @@
           <t>GODI India</t>
         </is>
       </c>
-      <c r="D9" s="44" t="inlineStr">
+      <c r="D9" s="47" t="inlineStr">
         <is>
           <t>https://evreporter.com/godi-receives-bis-certification-to-sell-li-ion-cells-in-india/</t>
         </is>
       </c>
-      <c r="E9" s="45" t="n">
+      <c r="E9" s="48" t="n">
         <v>700</v>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Camera</t>
         </is>
@@ -2872,17 +2903,17 @@
           <t>Robu.in</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="47" t="inlineStr">
         <is>
           <t>https://robu.in/product/arducam-12mp-imx477-motorized-focus-high-quality-camera-for-raspberry-pi/</t>
         </is>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="48" t="n">
         <v>9600</v>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>GNSS RTK</t>
         </is>
@@ -2897,17 +2928,17 @@
           <t>Teravolt Labs</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="47" t="inlineStr">
         <is>
           <t>https://www.teravolt.in/product-page/aeronav-1-dual-band-gnss</t>
         </is>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="48" t="n">
         <v>18000</v>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="46" t="inlineStr">
         <is>
           <t>AI accelerator</t>
         </is>
@@ -2922,46 +2953,46 @@
           <t>Robu.in</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="47" t="inlineStr">
         <is>
           <t>https://robu.in/product/raspberry-pi-ai-hat-26-tops/</t>
         </is>
       </c>
-      <c r="E12" s="45" t="inlineStr">
+      <c r="E12" s="48" t="inlineStr">
         <is>
           <t>confirm</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="46" t="inlineStr">
+      <c r="A13" s="49" t="inlineStr">
         <is>
           <t>Sub-GHz radio (deferred)</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>RFDesign RFD 868ux-IND, 865-870 MHz</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>XBOOM India</t>
         </is>
       </c>
-      <c r="D13" s="47" t="inlineStr">
+      <c r="D13" s="50" t="inlineStr">
         <is>
           <t>https://www.xboom.in/shop/drones/drone-components/transmission/rfd-868ux-ind-long-range-modem-bundle/</t>
         </is>
       </c>
-      <c r="E13" s="48" t="inlineStr">
+      <c r="E13" s="51" t="inlineStr">
         <is>
           <t>confirm</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="46" t="inlineStr">
         <is>
           <t>Co-processor</t>
         </is>
@@ -2976,12 +3007,12 @@
           <t>C-DAC (MeitY)</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="47" t="inlineStr">
         <is>
           <t>https://vegaprocessors.in/</t>
         </is>
       </c>
-      <c r="E14" s="45" t="n">
+      <c r="E14" s="48" t="n">
         <v>0</v>
       </c>
     </row>

--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1397,35 +1397,62 @@
       </c>
       <c r="F19" s="10" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="30" t="n"/>
-      <c r="B20" s="31" t="inlineStr">
-        <is>
-          <t>TOTAL PER AIRCRAFT</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="32">
-        <f>SUM(E5:E19)</f>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>VEGA co-processor</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="24">
+        <f>C20*D20</f>
         <v/>
       </c>
-      <c r="F20" s="30" t="n"/>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>C-DAC ARIES v3.0. Free to top-100 teams, so it costs nothing to carry. A monitor and logger, NOT an accelerator -- RV32IM at 100 MHz with 256 KB SRAM. Retained because it is the only Indian silicon on the aircraft and the indigenisation claim in Section VIII depends on it.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="n"/>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>x3 FLEET</t>
+          <t>TOTAL PER AIRCRAFT</t>
         </is>
       </c>
       <c r="C21" s="30" t="n"/>
       <c r="D21" s="30" t="n"/>
       <c r="E21" s="32">
-        <f>E20*3</f>
+        <f>SUM(E5:E20)</f>
         <v/>
       </c>
       <c r="F21" s="30" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="n"/>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>x3 FLEET</t>
+        </is>
+      </c>
+      <c r="C22" s="30" t="n"/>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="32">
+        <f>E21*3</f>
+        <v/>
+      </c>
+      <c r="F22" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -1241,7 +1241,11 @@
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="10" t="inlineStr"/>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>ExpressLRS receiver MUST run 3.5+ in NATIVE MAVLink mode. That mode carries RC control and MAVLink on ONE link and one autopilot UART, which is what allows the sub-GHz safety radio to be deferred. The older AirPort mode is a transparent serial bridge that CONSUMES the link -- configured that way the aircraft has telemetry and no control, and needs the second radio back. Not a preference; the deferral depends on it.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="26" t="inlineStr">

--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>653260</v>
+        <v>638760</v>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>466000</v>
+        <v>451500</v>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="inlineStr">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>107488</v>
+        <v>105313</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10" t="inlineStr">
@@ -815,12 +815,12 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>824072</v>
+        <v>807397</v>
       </c>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>8.24 lakh</t>
+          <t>8.07 lakh</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>354000</v>
+        <v>417000</v>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="10" t="inlineStr">
@@ -1758,46 +1758,46 @@
       </c>
     </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="9" t="n"/>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="A16" s="41" t="n"/>
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>Equipment cases</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="24" t="n">
         <v>44000</v>
       </c>
-      <c r="D16" s="29" t="n">
-        <v>9000</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>-35000</v>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>One aircraft case, two foam-lined crates.</t>
+      <c r="D16" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>-44000</v>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>R1: CONFIRMED HELD by the institute, 2026-08-18. Department stores.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="27" t="inlineStr">
+      <c r="A17" s="41" t="n"/>
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>Fire extinguisher, sand, charging bags</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="24" t="n">
         <v>11000</v>
       </c>
-      <c r="D17" s="29" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>-7000</v>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>KEEP THE CAPABILITY, correct the price. 54 Li-ion cells are cycled across this programme; thermal runaway is a real failure mode.</t>
+      <c r="D17" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>R1: CONFIRMED HELD by the institute, 2026-08-18. Safety office. The capability is still required -- 54 Li-ion cells are cycled across this programme and thermal runaway is a real failure mode -- it is simply no longer being bought.</t>
         </is>
       </c>
     </row>
@@ -2056,24 +2056,24 @@
       </c>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="27" t="inlineStr">
+      <c r="A30" s="41" t="n"/>
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>Charger PSU</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="24" t="n">
         <v>8000</v>
       </c>
-      <c r="D30" s="29" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E30" s="35" t="n">
-        <v>-6500</v>
-      </c>
-      <c r="F30" s="10" t="inlineStr">
-        <is>
-          <t>Used 12 V server supply.</t>
+      <c r="D30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="42" t="n">
+        <v>-8000</v>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>R1: CONFIRMED HELD by the institute, 2026-08-18.</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="32" t="n">
-        <v>653260</v>
+        <v>638760</v>
       </c>
       <c r="E48" s="30" t="n"/>
       <c r="F48" s="30" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C51" s="30" t="n"/>
       <c r="D51" s="32" t="n">
-        <v>107488</v>
+        <v>105313</v>
       </c>
       <c r="E51" s="30" t="n"/>
       <c r="F51" s="30" t="n"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C52" s="30" t="n"/>
       <c r="D52" s="32" t="n">
-        <v>824072</v>
+        <v>807397</v>
       </c>
       <c r="E52" s="30" t="n"/>
       <c r="F52" s="30" t="n"/>

--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>638760</v>
+        <v>581900</v>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>451500</v>
+        <v>405100</v>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="inlineStr">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>182260</v>
+        <v>171800</v>
       </c>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="10" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>25863</v>
+        <v>24378</v>
       </c>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="10" t="inlineStr">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C18" s="12" t="n">
-        <v>37462</v>
+        <v>35312</v>
       </c>
       <c r="D18" s="13" t="n"/>
       <c r="E18" s="14" t="inlineStr">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>105313</v>
+        <v>96239</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10" t="inlineStr">
@@ -815,12 +815,12 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>807397</v>
+        <v>737829</v>
       </c>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>8.07 lakh</t>
+          <t>7.38 lakh</t>
         </is>
       </c>
     </row>
@@ -1570,46 +1570,46 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="A7" s="36" t="n"/>
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>Relief kits (14)</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="38" t="n">
         <v>5600</v>
       </c>
-      <c r="D7" s="29" t="n">
-        <v>5600</v>
-      </c>
-      <c r="E7" s="35" t="n">
+      <c r="D7" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>Rule C6 fixes the kit at 200 g.</t>
+      <c r="E7" s="39" t="n">
+        <v>-5600</v>
+      </c>
+      <c r="F7" s="40" t="inlineStr">
+        <is>
+          <t>DEFERRED AT TEAM DIRECTION 2026-08-18. Rule C6 fixes the kit at 200 g. THIS IS THE DELIVERED PAYLOAD -- see the note in the deferred register.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="27" t="inlineStr">
+      <c r="A8" s="36" t="n"/>
+      <c r="B8" s="37" t="inlineStr">
         <is>
           <t>Ground-truth apparatus</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="38" t="n">
         <v>35280</v>
       </c>
-      <c r="D8" s="29" t="n">
-        <v>4860</v>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>-30420</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>R5. Mannequins, mats, markers, clothing and dummy kits all fabricated. Dummy kits and clothing are BETTER made than bought -- exact 200 g mass, and wider colour variety than matched sets.</t>
+      <c r="D8" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>-35280</v>
+      </c>
+      <c r="F8" s="40" t="inlineStr">
+        <is>
+          <t>DEFERRED AT TEAM DIRECTION 2026-08-18. Was R5, fabricated. Removing it means detection has no target to be measured against, so recall stays modelled -- the field-data campaign is deferred too.</t>
         </is>
       </c>
     </row>
@@ -2112,46 +2112,46 @@
       <c r="F32" s="34" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="9" t="n"/>
-      <c r="B33" s="27" t="inlineStr">
+      <c r="A33" s="36" t="n"/>
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>Spare airframe structure set</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="38" t="n">
         <v>25000</v>
       </c>
-      <c r="D33" s="29" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E33" s="35" t="n">
+      <c r="D33" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="10" t="inlineStr">
-        <is>
-          <t>KEEP. What a crash consumes.</t>
+      <c r="E33" s="39" t="n">
+        <v>-25000</v>
+      </c>
+      <c r="F33" s="40" t="inlineStr">
+        <is>
+          <t>DEFERRED AT TEAM DIRECTION 2026-08-18. This was the crash cover.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="9" t="n"/>
-      <c r="B34" s="27" t="inlineStr">
+      <c r="A34" s="36" t="n"/>
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>Spare propellers, plate and tube stock</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="38" t="n">
         <v>26200</v>
       </c>
-      <c r="D34" s="29" t="n">
-        <v>21400</v>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>-4800</v>
-      </c>
-      <c r="F34" s="10" t="inlineStr">
-        <is>
-          <t>KEEP. Consumables.</t>
+      <c r="D34" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="39" t="n">
+        <v>-26200</v>
+      </c>
+      <c r="F34" s="40" t="inlineStr">
+        <is>
+          <t>DEFERRED AT TEAM DIRECTION 2026-08-18. Propellers are the most frequently consumed item in a flight-test campaign.</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="32" t="n">
-        <v>638760</v>
+        <v>581900</v>
       </c>
       <c r="E48" s="30" t="n"/>
       <c r="F48" s="30" t="n"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C49" s="30" t="n"/>
       <c r="D49" s="32" t="n">
-        <v>25863</v>
+        <v>24378</v>
       </c>
       <c r="E49" s="30" t="n"/>
       <c r="F49" s="30" t="n"/>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C50" s="30" t="n"/>
       <c r="D50" s="32" t="n">
-        <v>37462</v>
+        <v>35312</v>
       </c>
       <c r="E50" s="30" t="n"/>
       <c r="F50" s="30" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="C51" s="30" t="n"/>
       <c r="D51" s="32" t="n">
-        <v>105313</v>
+        <v>96239</v>
       </c>
       <c r="E51" s="30" t="n"/>
       <c r="F51" s="30" t="n"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C52" s="30" t="n"/>
       <c r="D52" s="32" t="n">
-        <v>807397</v>
+        <v>737829</v>
       </c>
       <c r="E52" s="30" t="n"/>
       <c r="F52" s="30" t="n"/>
@@ -2521,7 +2521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2710,17 +2710,89 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="30" t="n"/>
-      <c r="B13" s="31" t="inlineStr">
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Spare airframe structure set</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. Was the crash cover; one hard landing now ends the campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Spare propellers and stock</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="n">
+        <v>21400</v>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. Propellers are the most consumed item in flight test</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Relief kits (14)</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>5600</v>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. THE DELIVERED PAYLOAD. Rule C6 fixes it at 200 g; without kits there is nothing to release and the delivery task scores nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>Ground-truth apparatus</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>4860</v>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Deferred 2026-08-18. Detection recall now has no target to be measured against</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="31" t="inlineStr">
         <is>
           <t>TOTAL DEFERRED</t>
         </is>
       </c>
-      <c r="C13" s="32" t="n">
-        <v>316770</v>
-      </c>
-      <c r="D13" s="30" t="n"/>
+      <c r="C17" s="32" t="n">
+        <v>373630</v>
+      </c>
+      <c r="D17" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/hardware/bom/RescueSwarm_Cost_Study.xlsx
+++ b/hardware/bom/RescueSwarm_Cost_Study.xlsx
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>157800</v>
+        <v>165800</v>
       </c>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="10" t="inlineStr">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>473400</v>
+        <v>497400</v>
       </c>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="10" t="inlineStr"/>
@@ -719,7 +719,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>581900</v>
+        <v>605900</v>
       </c>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="10" t="inlineStr">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>405100</v>
+        <v>429100</v>
       </c>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="10" t="inlineStr">
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>96239</v>
+        <v>99839</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="10" t="inlineStr">
@@ -815,12 +815,12 @@
         </is>
       </c>
       <c r="C20" s="12" t="n">
-        <v>737829</v>
+        <v>765429</v>
       </c>
       <c r="D20" s="13" t="n"/>
       <c r="E20" s="14" t="inlineStr">
         <is>
-          <t>7.38 lakh</t>
+          <t>7.65 lakh</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -965,7 +965,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adopted air vehicle - 157,800 per aircraft</t>
+          <t>Adopted air vehicle - 165,800 per aircraft</t>
         </is>
       </c>
     </row>
@@ -1043,14 +1043,14 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>AI accelerator</t>
+          <t>Companion computer</t>
         </is>
       </c>
       <c r="C6" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="24" t="n">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="E6" s="24">
         <f>C6*D6</f>
@@ -1058,7 +1058,7 @@
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>26 TOPS. The specification floor, not a preference.</t>
+          <t>Raspberry Pi 5 8 GB. THE HOST THE AUTONOMY RUNS ON -- Linux, ROS 2, the coverage planner, MAVLink routing, the mesh link and the delivery logic. It was missing: the accelerator below is a Pi AI HAT+, which communicates over the Pi 5's PCIe and is an M.2 card with nothing to plug into without it, and the camera is a CSI module with nothing to connect to. The verified BOM carried a 55,000 module WITH an integrated host; the cost pass swapped in a 20,000 accelerator and did not put the host back.</t>
         </is>
       </c>
     </row>
@@ -1070,14 +1070,14 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>GNSS RTK primary</t>
+          <t>AI accelerator</t>
         </is>
       </c>
       <c r="C7" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="E7" s="24">
         <f>C7*D7</f>
@@ -1085,61 +1085,61 @@
       </c>
       <c r="F7" s="25" t="inlineStr">
         <is>
-          <t>No cheaper RTK-capable part exists. Governs 125 of 200 geotag points.</t>
+          <t>26 TOPS. The specification floor, not a preference. Pi AI HAT+ (Hailo-8) -- an NPU, not a computer; needs the host above.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>hobby</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Motors</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E8" s="29">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>GNSS RTK primary</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E8" s="24">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Generic 5008-class. NO PUBLISHED THRUST -- verify on the thrust stand.</t>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>No cheaper RTK-capable part exists. Governs 125 of 200 geotag points.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
-        <is>
-          <t>KEEP</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Li-ion cells</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="n">
-        <v>18</v>
-      </c>
-      <c r="D9" s="24" t="n">
-        <v>700</v>
-      </c>
-      <c r="E9" s="24">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>hobby</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Motors</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>4500</v>
+      </c>
+      <c r="E9" s="29">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="25" t="inlineStr">
-        <is>
-          <t>Capacity- and IR-matched. One weak cell defines the whole pack.</t>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Generic 5008-class. NO PUBLISHED THRUST -- verify on the thrust stand.</t>
         </is>
       </c>
     </row>
@@ -1151,14 +1151,14 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Li-ion cells</t>
         </is>
       </c>
       <c r="C10" s="23" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D10" s="24" t="n">
-        <v>13000</v>
+        <v>700</v>
       </c>
       <c r="E10" s="24">
         <f>C10*D10</f>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>In-house fabrication; institute machine shop confirmed.</t>
+          <t>Capacity- and IR-matched. One weak cell defines the whole pack.</t>
         </is>
       </c>
     </row>
@@ -1178,14 +1178,14 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Camera + lens</t>
+          <t>Structure</t>
         </is>
       </c>
       <c r="C11" s="23" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>11100</v>
+        <v>13000</v>
       </c>
       <c r="E11" s="24">
         <f>C11*D11</f>
@@ -1193,32 +1193,36 @@
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>Arducam IMX477 + 6 mm. Pi-compatible; GSD drives detection.</t>
+          <t>In-house fabrication; institute machine shop confirmed.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>hobby</t>
-        </is>
-      </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Pack, BMS, PDB, BEC</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="n">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Camera + lens</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="29" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E12" s="29">
+      <c r="D12" s="24" t="n">
+        <v>11100</v>
+      </c>
+      <c r="E12" s="24">
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="F12" s="10" t="inlineStr"/>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>Arducam IMX477 + 6 mm. Pi-compatible; GSD drives detection.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="26" t="inlineStr">
@@ -1228,7 +1232,7 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>RC rx, storage, cooling, mounts</t>
+          <t>Pack, BMS, PDB, BEC</t>
         </is>
       </c>
       <c r="C13" s="28" t="n">
@@ -1241,11 +1245,7 @@
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>ExpressLRS receiver MUST run 3.5+ in NATIVE MAVLink mode. That mode carries RC control and MAVLink on ONE link and one autopilot UART, which is what allows the sub-GHz safety radio to be deferred. The older AirPort mode is a transparent serial bridge that CONSUMES the link -- configured that way the aircraft has telemetry and no control, and needs the second radio back. Not a preference; the deferral depends on it.</t>
-        </is>
-      </c>
+      <c r="F13" s="10" t="inlineStr"/>
     </row>
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="26" t="inlineStr">
@@ -1255,14 +1255,14 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>ESCs</t>
+          <t>RC rx, storage, cooling, mounts</t>
         </is>
       </c>
       <c r="C14" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>1800</v>
+        <v>8500</v>
       </c>
       <c r="E14" s="29">
         <f>C14*D14</f>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>Generic 60 A. Rating is easy to verify.</t>
+          <t>ExpressLRS receiver MUST run 3.5+ in NATIVE MAVLink mode. That mode carries RC control and MAVLink on ONE link and one autopilot UART, which is what allows the sub-GHz safety radio to be deferred. The older AirPort mode is a transparent serial bridge that CONSUMES the link -- configured that way the aircraft has telemetry and no control, and needs the second radio back. Not a preference; the deferral depends on it.</t>
         </is>
       </c>
     </row>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>Mesh node + antennas</t>
+          <t>ESCs</t>
         </is>
       </c>
       <c r="C15" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>6000</v>
+        <v>1800</v>
       </c>
       <c r="E15" s="29">
         <f>C15*D15</f>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>Rule 8.14: three concurrent feeds.</t>
+          <t>Generic 60 A. Rating is easy to verify.</t>
         </is>
       </c>
     </row>
@@ -1309,14 +1309,14 @@
       </c>
       <c r="B16" s="27" t="inlineStr">
         <is>
-          <t>Payload system</t>
+          <t>Mesh node + antennas</t>
         </is>
       </c>
       <c r="C16" s="28" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>4500</v>
+        <v>6000</v>
       </c>
       <c r="E16" s="29">
         <f>C16*D16</f>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>Metal detents retained -- a brownout must not drop a kit.</t>
+          <t>Rule 8.14: three concurrent feeds.</t>
         </is>
       </c>
     </row>
@@ -1336,14 +1336,14 @@
       </c>
       <c r="B17" s="27" t="inlineStr">
         <is>
-          <t>Propellers</t>
+          <t>Payload system</t>
         </is>
       </c>
       <c r="C17" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="29" t="n">
-        <v>1000</v>
+        <v>4500</v>
       </c>
       <c r="E17" s="29">
         <f>C17*D17</f>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>Generic 18 in CF. Balance every one.</t>
+          <t>Metal detents retained -- a brownout must not drop a kit.</t>
         </is>
       </c>
     </row>
@@ -1363,20 +1363,24 @@
       </c>
       <c r="B18" s="27" t="inlineStr">
         <is>
-          <t>Wiring, connectors</t>
+          <t>Propellers</t>
         </is>
       </c>
       <c r="C18" s="28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>2400</v>
+        <v>1000</v>
       </c>
       <c r="E18" s="29">
         <f>C18*D18</f>
         <v/>
       </c>
-      <c r="F18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Generic 18 in CF. Balance every one.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
@@ -1386,14 +1390,14 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>Prop adapters</t>
+          <t>Wiring, connectors</t>
         </is>
       </c>
       <c r="C19" s="28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D19" s="29" t="n">
-        <v>350</v>
+        <v>2400</v>
       </c>
       <c r="E19" s="29">
         <f>C19*D19</f>
@@ -1402,61 +1406,84 @@
       <c r="F19" s="10" t="inlineStr"/>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>KEEP</t>
-        </is>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>VEGA co-processor</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="24">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>hobby</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>Prop adapters</t>
+        </is>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>350</v>
+      </c>
+      <c r="E20" s="29">
         <f>C20*D20</f>
         <v/>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>VEGA co-processor</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="24">
+        <f>C21*D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>C-DAC ARIES v3.0. Free to top-100 teams, so it costs nothing to carry. A monitor and logger, NOT an accelerator -- RV32IM at 100 MHz with 256 KB SRAM. Retained because it is the only Indian silicon on the aircraft and the indigenisation claim in Section VIII depends on it.</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="30" t="n"/>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>TOTAL PER AIRCRAFT</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="32">
-        <f>SUM(E5:E20)</f>
-        <v/>
-      </c>
-      <c r="F21" s="30" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="30" t="n"/>
       <c r="B22" s="31" t="inlineStr">
         <is>
-          <t>x3 FLEET</t>
+          <t>TOTAL PER AIRCRAFT</t>
         </is>
       </c>
       <c r="C22" s="30" t="n"/>
       <c r="D22" s="30" t="n"/>
       <c r="E22" s="32">
-        <f>E21*3</f>
+        <f>SUM(E5:E21)</f>
         <v/>
       </c>
       <c r="F22" s="30" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>x3 FLEET</t>
+        </is>
+      </c>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="32">
+        <f>E22*3</f>
+        <v/>
+      </c>
+      <c r="F23" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1551,17 +1578,17 @@
       <c r="A6" s="9" t="n"/>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Air vehicles, 3 x 157,800</t>
+          <t>Air vehicles, 3 x 165,800</t>
         </is>
       </c>
       <c r="C6" s="29" t="n">
         <v>790203</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>473400</v>
+        <v>497400</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>-316803</v>
+        <v>-292803</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
@@ -2440,7 +2467,7 @@
       </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="32" t="n">
-        <v>581900</v>
+        <v>605900</v>
       </c>
       <c r="E48" s="30" t="n"/>
       <c r="F48" s="30" t="n"/>
@@ -2482,7 +2509,7 @@
       </c>
       <c r="C51" s="30" t="n"/>
       <c r="D51" s="32" t="n">
-        <v>96239</v>
+        <v>99839</v>
       </c>
       <c r="E51" s="30" t="n"/>
       <c r="F51" s="30" t="n"/>
@@ -2496,7 +2523,7 @@
       </c>
       <c r="C52" s="30" t="n"/>
       <c r="D52" s="32" t="n">
-        <v>737829</v>
+        <v>765429</v>
       </c>
       <c r="E52" s="30" t="n"/>
       <c r="F52" s="30" t="n"/>
